--- a/tools.xlsx
+++ b/tools.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coldtec-my.sharepoint.com/personal/marcel_niederer_coldtec_ch/Documents/1_IT/1_Projekte/Claude/Linkübersicht/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_8CFF6D7E14DC6ED290B46A3F77B8FBAA30B55BE7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1809D00B-5748-488F-B440-8E200178A540}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_8CFF6D7E14DC6ED290B46A3F77B8FBAA30B55BE7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A74747D9-D19D-46B7-8B08-9CB3EE6401F8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,15 +46,9 @@
     <t>Einkauf</t>
   </si>
   <si>
-    <t>Voraussichtlicher LT für deaktivierte Artikel von BSH</t>
-  </si>
-  <si>
     <t>https://coldtec.github.io/vorlage_artikelimport/</t>
   </si>
   <si>
-    <t>Vorlage Artikelimport erstellen</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://marsl21.github.io/ArtNr/ </t>
   </si>
   <si>
@@ -91,9 +85,6 @@
     <t>https://marsl21.github.io/robbi/</t>
   </si>
   <si>
-    <t>Hilft die Artikel in die Masterliste zu übertragen</t>
-  </si>
-  <si>
     <t>https://marsl21.github.io/Verkaufstexte/</t>
   </si>
   <si>
@@ -101,6 +92,15 @@
   </si>
   <si>
     <t>Das Tool um die Verkaufstexte zu erstellen</t>
+  </si>
+  <si>
+    <t>Vorlage Artikelimport erstellen.</t>
+  </si>
+  <si>
+    <t>Voraussichtlicher Liefertermin für die deaktivierten Artikel bestimmen.</t>
+  </si>
+  <si>
+    <t>Robbi hilft die Artikel in die Masterliste zu übertragen</t>
   </si>
 </sst>
 </file>
@@ -181,6 +181,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -404,13 +408,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -424,35 +428,35 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -460,41 +464,41 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/tools.xlsx
+++ b/tools.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coldtec-my.sharepoint.com/personal/marcel_niederer_coldtec_ch/Documents/1_IT/1_Projekte/Claude/Linkübersicht/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coldtec-my.sharepoint.com/personal/marcel_niederer_coldtec_ch/Documents/1_IT/1_Projekte/Claude/Übersicht_Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_8CFF6D7E14DC6ED290B46A3F77B8FBAA30B55BE7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A74747D9-D19D-46B7-8B08-9CB3EE6401F8}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_8CFF6D7E14DC6ED290B46A3F77B8FBAA30B55BE7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2168517-8BFE-4555-A131-A42049DB05A4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tools" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>Name</t>
   </si>
@@ -101,6 +101,15 @@
   </si>
   <si>
     <t>Robbi hilft die Artikel in die Masterliste zu übertragen</t>
+  </si>
+  <si>
+    <t>Artikelvergleich</t>
+  </si>
+  <si>
+    <t>https://coldtec.github.io/Artikelvergleich/</t>
+  </si>
+  <si>
+    <t>Ist der Artikel auf dem Shop? (Artikelliste Shop-Abfrage und dein Excel hochladen und dann siehst du, ob der Artikel online ist oder nicht)</t>
   </si>
 </sst>
 </file>
@@ -380,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -501,6 +510,20 @@
         <v>23</v>
       </c>
     </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" tooltip="https://coldtec.github.io/BSH_deaktivierte/" xr:uid="{C3648183-8420-49C3-9452-DB9C339739DD}"/>
@@ -510,6 +533,7 @@
     <hyperlink ref="B7" r:id="rId5" xr:uid="{9A4FD7BB-50C7-4EA1-BFE1-B0378DFFE570}"/>
     <hyperlink ref="B4" r:id="rId6" xr:uid="{50A63998-A2BB-4727-8395-BBB57B974EF0}"/>
     <hyperlink ref="B8" r:id="rId7" xr:uid="{D8CE5032-363D-4D81-8E8A-52BB491F49BA}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{C634EF94-9804-474E-B6C3-5D691127A250}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
